--- a/카드_아키타입/01_토너·미스트.xlsx
+++ b/카드_아키타입/01_토너·미스트.xlsx
@@ -331,7 +331,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1581,7 +1581,7 @@
       <row>119</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>

--- a/카드_아키타입/01_토너·미스트.xlsx
+++ b/카드_아키타입/01_토너·미스트.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10248900"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10248900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10248900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="10248900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="14020800"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="23050500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="23050500"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="23050500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="23050500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="29845000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="29845000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="29845000"/>
     <ext cx="1809750" cy="1038225"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="29845000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>45</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>45</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>45</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="33540700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="37655500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="37655500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="37655500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>55</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="37655500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>55</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>55</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>55</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>55</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>55</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="41351200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>55</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="41351200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>67</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="43275250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>67</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="43275250"/>
     <ext cx="1533525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>67</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="43275250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>67</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="43275250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>67</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>67</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>67</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>67</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>67</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="46970950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>67</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="46970950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="49256950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="49256950"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="49256950"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="49256950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="51104800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="51104800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>79</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="51104800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="57067450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="57067450"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="57067450"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="57067450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58915300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>92</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58915300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="62236350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="62236350"/>
     <ext cx="1371600" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="62236350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>105</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="62236350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>105</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="64084200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="70046850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="70046850"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="70046850"/>
     <ext cx="1809750" cy="476250"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="70046850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71894700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71894700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="77450950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="77450950"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="77450950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="77450950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="79298799"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="85261450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="85261450"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="85261450"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="85261450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>144</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="87109300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>144</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="87109300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="93478350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="93478350"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="93478350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="93478350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>158</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="95326200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="104336850"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="104336850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="104336850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="104336850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="114585750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="114585750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="114585750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="114585750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="120973850"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="120973850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="120973850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>194</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="120973850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="126345950"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="126345950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="126345950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="126345950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>217</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="131514850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>217</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="131514850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>217</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="131514850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>217</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="131514850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="138715750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="138715750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="138715750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="138715750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="146119850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="146119850"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="146119850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="146119850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="147967700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="154336750"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="154336750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="154336750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="154336750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="159099250"/>
     <ext cx="1809750" cy="1247775"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="159099250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="159099250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="159099250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>278</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="162642550"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>278</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="162642550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>278</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="162642550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>278</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="162642550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="165779450"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="165779450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="165779450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="165779450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>288</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="167627300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>288</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="167627300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>298</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="175418750"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>298</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="175418750"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>298</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="175418750"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>298</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="175418750"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>298</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>298</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>298</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>298</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>298</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="179114450"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>298</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="179114450"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>298</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="179114450"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>311</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>311</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="182886350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>322</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="191693800"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>322</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="191693800"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="197065900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="197065900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="197065900"/>
     <ext cx="1809750" cy="400050"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>333</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="197065900"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>345</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="207111600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>345</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="207111600"/>
     <ext cx="1809750" cy="1581150"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>345</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="207111600"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>356</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="214312500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>356</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="214312500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>356</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="214312500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>356</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="214312500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>356</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="216160350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>371</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="221107000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>371</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="221107000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>371</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="221107000"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>371</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="221107000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>371</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>371</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>371</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>371</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>371</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="224802700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>385</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="228714300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>385</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="228714300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>385</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="228714300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>385</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="228714300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>385</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="230562150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>397</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="236321600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>397</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="236321600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>397</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="236321600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>397</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="236321600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>409</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="244335300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>409</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="244335300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>409</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="244335300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>409</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="244335300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="251333000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="251333000"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="251333000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>421</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="251333000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>421</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="253180850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>435</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="258127500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>435</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="258127500"/>
     <ext cx="1809750" cy="1143000"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>435</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="258127500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>435</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="258127500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>435</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="259975350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>447</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="271627600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>447</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="271627600"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>447</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="271627600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>447</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="271627600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>447</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="273475450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>459</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="278828500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>459</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="278828500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>459</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="278828500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>459</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="278828500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>459</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="280676350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>471</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="287248600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>471</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="287248600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>471</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="287248600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>471</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="287248600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>471</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="289096450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>471</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="289096450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>471</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="289096450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>484</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="296481500"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>484</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="296481500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>484</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="296481500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>484</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="296481500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>498</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="306324000"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>507</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="310502300"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>518</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="314858400"/>
     <ext cx="1152525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>526</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="317817500"/>
     <ext cx="1543050" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>536</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="323011800"/>
     <ext cx="1152525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>548</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="331431900"/>
     <ext cx="1066800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>562</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="341477600"/>
     <ext cx="1238250" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="346036900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="346036900"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="346036900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="346036900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>572</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="347884750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="357708200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="357708200"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="357708200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>586</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="357708200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>586</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="359556050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>598</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="367550700"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>611</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="373532400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>611</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="373532400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>611</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="373532400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>611</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="373532400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="378701300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="378701300"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="378701300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="378701300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>622</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="380549150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>634</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>634</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>634</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>634</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6398,7 +5158,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/01_토너·미스트.xlsx
+++ b/카드_아키타입/01_토너·미스트.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10248900"/>
+    <pos x="7391400" y="10248900"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10248900"/>
+    <pos x="9239250" y="10248900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10248900"/>
+    <pos x="11087100" y="10248900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="10248900"/>
+    <pos x="12934950" y="10248900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="14020800"/>
+    <pos x="7391400" y="14020800"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="23050500"/>
+    <pos x="7391400" y="23050500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="23050500"/>
+    <pos x="9239250" y="23050500"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="23050500"/>
+    <pos x="11087100" y="23050500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="23050500"/>
+    <pos x="12934950" y="23050500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="24898350"/>
+    <pos x="7391400" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="24898350"/>
+    <pos x="9239250" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="24898350"/>
+    <pos x="11087100" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="24898350"/>
+    <pos x="12934950" y="24898350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="29845000"/>
+    <pos x="7391400" y="29845000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="29845000"/>
+    <pos x="9239250" y="29845000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="29845000"/>
+    <pos x="11087100" y="29845000"/>
     <ext cx="1809750" cy="1038225"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="29845000"/>
+    <pos x="12934950" y="29845000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="31692850"/>
+    <pos x="7391400" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="31692850"/>
+    <pos x="9239250" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="31692850"/>
+    <pos x="11087100" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="31692850"/>
+    <pos x="12934950" y="31692850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="33540700"/>
+    <pos x="7391400" y="33540700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="37655500"/>
+    <pos x="7391400" y="37655500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="37655500"/>
+    <pos x="9239250" y="37655500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="37655500"/>
+    <pos x="11087100" y="37655500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="37655500"/>
+    <pos x="12934950" y="37655500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="39503350"/>
+    <pos x="7391400" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="39503350"/>
+    <pos x="9239250" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="39503350"/>
+    <pos x="11087100" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="39503350"/>
+    <pos x="12934950" y="39503350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="41351200"/>
+    <pos x="7391400" y="41351200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="41351200"/>
+    <pos x="9239250" y="41351200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="43275250"/>
+    <pos x="7391400" y="43275250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="43275250"/>
+    <pos x="9239250" y="43275250"/>
     <ext cx="1533525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="43275250"/>
+    <pos x="11087100" y="43275250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="43275250"/>
+    <pos x="12934950" y="43275250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="45123100"/>
+    <pos x="7391400" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="45123100"/>
+    <pos x="9239250" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="45123100"/>
+    <pos x="11087100" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="45123100"/>
+    <pos x="12934950" y="45123100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="46970950"/>
+    <pos x="7391400" y="46970950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="46970950"/>
+    <pos x="9239250" y="46970950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="49256950"/>
+    <pos x="7391400" y="49256950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="49256950"/>
+    <pos x="9239250" y="49256950"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="49256950"/>
+    <pos x="11087100" y="49256950"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="49256950"/>
+    <pos x="12934950" y="49256950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="51104800"/>
+    <pos x="7391400" y="51104800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="51104800"/>
+    <pos x="9239250" y="51104800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="51104800"/>
+    <pos x="11087100" y="51104800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="57067450"/>
+    <pos x="7391400" y="57067450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="57067450"/>
+    <pos x="9239250" y="57067450"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="57067450"/>
+    <pos x="11087100" y="57067450"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="57067450"/>
+    <pos x="12934950" y="57067450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58915300"/>
+    <pos x="7391400" y="58915300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58915300"/>
+    <pos x="9239250" y="58915300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="62236350"/>
+    <pos x="7391400" y="62236350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="62236350"/>
+    <pos x="9239250" y="62236350"/>
     <ext cx="1371600" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="62236350"/>
+    <pos x="11087100" y="62236350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="62236350"/>
+    <pos x="12934950" y="62236350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="64084200"/>
+    <pos x="7391400" y="64084200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="70046850"/>
+    <pos x="7391400" y="70046850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="70046850"/>
+    <pos x="9239250" y="70046850"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="70046850"/>
+    <pos x="11087100" y="70046850"/>
     <ext cx="1809750" cy="476250"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="70046850"/>
+    <pos x="12934950" y="70046850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71894700"/>
+    <pos x="7391400" y="71894700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71894700"/>
+    <pos x="9239250" y="71894700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="77450950"/>
+    <pos x="7391400" y="77450950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="77450950"/>
+    <pos x="9239250" y="77450950"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="77450950"/>
+    <pos x="11087100" y="77450950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="77450950"/>
+    <pos x="12934950" y="77450950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="79298799"/>
+    <pos x="7391400" y="79298799"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="85261450"/>
+    <pos x="7391400" y="85261450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="85261450"/>
+    <pos x="9239250" y="85261450"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="85261450"/>
+    <pos x="11087100" y="85261450"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="85261450"/>
+    <pos x="12934950" y="85261450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="87109300"/>
+    <pos x="7391400" y="87109300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="87109300"/>
+    <pos x="9239250" y="87109300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="93478350"/>
+    <pos x="7391400" y="93478350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="93478350"/>
+    <pos x="9239250" y="93478350"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="93478350"/>
+    <pos x="11087100" y="93478350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="93478350"/>
+    <pos x="12934950" y="93478350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="95326200"/>
+    <pos x="7391400" y="95326200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="104336850"/>
+    <pos x="7391400" y="104336850"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="104336850"/>
+    <pos x="9239250" y="104336850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="104336850"/>
+    <pos x="11087100" y="104336850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="104336850"/>
+    <pos x="12934950" y="104336850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="114585750"/>
+    <pos x="7391400" y="114585750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="114585750"/>
+    <pos x="9239250" y="114585750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="114585750"/>
+    <pos x="11087100" y="114585750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="114585750"/>
+    <pos x="12934950" y="114585750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="120973850"/>
+    <pos x="7391400" y="120973850"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="120973850"/>
+    <pos x="9239250" y="120973850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="120973850"/>
+    <pos x="11087100" y="120973850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="120973850"/>
+    <pos x="12934950" y="120973850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="126345950"/>
+    <pos x="7391400" y="126345950"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="126345950"/>
+    <pos x="9239250" y="126345950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="126345950"/>
+    <pos x="11087100" y="126345950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="126345950"/>
+    <pos x="12934950" y="126345950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="131514850"/>
+    <pos x="7391400" y="131514850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="131514850"/>
+    <pos x="9239250" y="131514850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="131514850"/>
+    <pos x="11087100" y="131514850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="131514850"/>
+    <pos x="12934950" y="131514850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="138715750"/>
+    <pos x="7391400" y="138715750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="138715750"/>
+    <pos x="9239250" y="138715750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="138715750"/>
+    <pos x="11087100" y="138715750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="138715750"/>
+    <pos x="12934950" y="138715750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="146119850"/>
+    <pos x="7391400" y="146119850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="146119850"/>
+    <pos x="9239250" y="146119850"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="146119850"/>
+    <pos x="11087100" y="146119850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="146119850"/>
+    <pos x="12934950" y="146119850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="147967700"/>
+    <pos x="7391400" y="147967700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="154336750"/>
+    <pos x="7391400" y="154336750"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="154336750"/>
+    <pos x="9239250" y="154336750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="154336750"/>
+    <pos x="11087100" y="154336750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="154336750"/>
+    <pos x="12934950" y="154336750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="159099250"/>
+    <pos x="7391400" y="159099250"/>
     <ext cx="1809750" cy="1247775"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="159099250"/>
+    <pos x="9239250" y="159099250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="159099250"/>
+    <pos x="11087100" y="159099250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="159099250"/>
+    <pos x="12934950" y="159099250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="162642550"/>
+    <pos x="7391400" y="162642550"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="162642550"/>
+    <pos x="9239250" y="162642550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="162642550"/>
+    <pos x="11087100" y="162642550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="162642550"/>
+    <pos x="12934950" y="162642550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="165779450"/>
+    <pos x="7391400" y="165779450"/>
     <ext cx="1257300" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="165779450"/>
+    <pos x="9239250" y="165779450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="165779450"/>
+    <pos x="11087100" y="165779450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="165779450"/>
+    <pos x="12934950" y="165779450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="167627300"/>
+    <pos x="7391400" y="167627300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="167627300"/>
+    <pos x="9239250" y="167627300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="175418750"/>
+    <pos x="7391400" y="175418750"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="175418750"/>
+    <pos x="9239250" y="175418750"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="175418750"/>
+    <pos x="11087100" y="175418750"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="175418750"/>
+    <pos x="12934950" y="175418750"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="177266600"/>
+    <pos x="7391400" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="177266600"/>
+    <pos x="9239250" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="177266600"/>
+    <pos x="11087100" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="177266600"/>
+    <pos x="12934950" y="177266600"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="179114450"/>
+    <pos x="7391400" y="179114450"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="179114450"/>
+    <pos x="9239250" y="179114450"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="179114450"/>
+    <pos x="11087100" y="179114450"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="181038500"/>
+    <pos x="7391400" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="181038500"/>
+    <pos x="9239250" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="181038500"/>
+    <pos x="11087100" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="181038500"/>
+    <pos x="12934950" y="181038500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="182886350"/>
+    <pos x="7391400" y="182886350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="191693800"/>
+    <pos x="7391400" y="191693800"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="191693800"/>
+    <pos x="9239250" y="191693800"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="197065900"/>
+    <pos x="7391400" y="197065900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="197065900"/>
+    <pos x="9239250" y="197065900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="197065900"/>
+    <pos x="11087100" y="197065900"/>
     <ext cx="1809750" cy="400050"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="197065900"/>
+    <pos x="12934950" y="197065900"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="207111600"/>
+    <pos x="7391400" y="207111600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="207111600"/>
+    <pos x="9239250" y="207111600"/>
     <ext cx="1809750" cy="1581150"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="207111600"/>
+    <pos x="11087100" y="207111600"/>
     <ext cx="1809750" cy="533400"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="214312500"/>
+    <pos x="7391400" y="214312500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="214312500"/>
+    <pos x="9239250" y="214312500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="214312500"/>
+    <pos x="11087100" y="214312500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="214312500"/>
+    <pos x="12934950" y="214312500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="216160350"/>
+    <pos x="7391400" y="216160350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="221107000"/>
+    <pos x="7391400" y="221107000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="221107000"/>
+    <pos x="9239250" y="221107000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="221107000"/>
+    <pos x="11087100" y="221107000"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="221107000"/>
+    <pos x="12934950" y="221107000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="222954850"/>
+    <pos x="7391400" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="222954850"/>
+    <pos x="9239250" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="222954850"/>
+    <pos x="11087100" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="222954850"/>
+    <pos x="12934950" y="222954850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="224802700"/>
+    <pos x="7391400" y="224802700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="228714300"/>
+    <pos x="7391400" y="228714300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="228714300"/>
+    <pos x="9239250" y="228714300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="228714300"/>
+    <pos x="11087100" y="228714300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="228714300"/>
+    <pos x="12934950" y="228714300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="230562150"/>
+    <pos x="7391400" y="230562150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="236321600"/>
+    <pos x="7391400" y="236321600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="236321600"/>
+    <pos x="9239250" y="236321600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="236321600"/>
+    <pos x="11087100" y="236321600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="236321600"/>
+    <pos x="12934950" y="236321600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="244335300"/>
+    <pos x="7391400" y="244335300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="244335300"/>
+    <pos x="9239250" y="244335300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="244335300"/>
+    <pos x="11087100" y="244335300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="244335300"/>
+    <pos x="12934950" y="244335300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="251333000"/>
+    <pos x="7391400" y="251333000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="251333000"/>
+    <pos x="9239250" y="251333000"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="251333000"/>
+    <pos x="11087100" y="251333000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="251333000"/>
+    <pos x="12934950" y="251333000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="253180850"/>
+    <pos x="7391400" y="253180850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="258127500"/>
+    <pos x="7391400" y="258127500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="258127500"/>
+    <pos x="9239250" y="258127500"/>
     <ext cx="1809750" cy="1143000"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="258127500"/>
+    <pos x="11087100" y="258127500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="258127500"/>
+    <pos x="12934950" y="258127500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="259975350"/>
+    <pos x="7391400" y="259975350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="271627600"/>
+    <pos x="7391400" y="271627600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="271627600"/>
+    <pos x="9239250" y="271627600"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="271627600"/>
+    <pos x="11087100" y="271627600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="271627600"/>
+    <pos x="12934950" y="271627600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="273475450"/>
+    <pos x="7391400" y="273475450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="278828500"/>
+    <pos x="7391400" y="278828500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="278828500"/>
+    <pos x="9239250" y="278828500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="278828500"/>
+    <pos x="11087100" y="278828500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="278828500"/>
+    <pos x="12934950" y="278828500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="280676350"/>
+    <pos x="7391400" y="280676350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="287248600"/>
+    <pos x="7391400" y="287248600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="287248600"/>
+    <pos x="9239250" y="287248600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="287248600"/>
+    <pos x="11087100" y="287248600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="287248600"/>
+    <pos x="12934950" y="287248600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="289096450"/>
+    <pos x="7391400" y="289096450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="289096450"/>
+    <pos x="9239250" y="289096450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="289096450"/>
+    <pos x="11087100" y="289096450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="296481500"/>
+    <pos x="7391400" y="296481500"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="296481500"/>
+    <pos x="9239250" y="296481500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="296481500"/>
+    <pos x="11087100" y="296481500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="296481500"/>
+    <pos x="12934950" y="296481500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="306324000"/>
+    <pos x="7391400" y="306324000"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="310502300"/>
+    <pos x="7391400" y="310502300"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="314858400"/>
+    <pos x="7391400" y="314858400"/>
     <ext cx="1152525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="317817500"/>
+    <pos x="7391400" y="317817500"/>
     <ext cx="1543050" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="323011800"/>
+    <pos x="7391400" y="323011800"/>
     <ext cx="1152525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="331431900"/>
+    <pos x="7391400" y="331431900"/>
     <ext cx="1066800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="341477600"/>
+    <pos x="7391400" y="341477600"/>
     <ext cx="1238250" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="346036900"/>
+    <pos x="7391400" y="346036900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="346036900"/>
+    <pos x="9239250" y="346036900"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="346036900"/>
+    <pos x="11087100" y="346036900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="346036900"/>
+    <pos x="12934950" y="346036900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="347884750"/>
+    <pos x="7391400" y="347884750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="357708200"/>
+    <pos x="7391400" y="357708200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="357708200"/>
+    <pos x="9239250" y="357708200"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="357708200"/>
+    <pos x="11087100" y="357708200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="357708200"/>
+    <pos x="12934950" y="357708200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="359556050"/>
+    <pos x="7391400" y="359556050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="367550700"/>
+    <pos x="7391400" y="367550700"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="373532400"/>
+    <pos x="7391400" y="373532400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="373532400"/>
+    <pos x="9239250" y="373532400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="373532400"/>
+    <pos x="11087100" y="373532400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="373532400"/>
+    <pos x="12934950" y="373532400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="378701300"/>
+    <pos x="7391400" y="378701300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="378701300"/>
+    <pos x="9239250" y="378701300"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="378701300"/>
+    <pos x="11087100" y="378701300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="378701300"/>
+    <pos x="12934950" y="378701300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="380549150"/>
+    <pos x="7391400" y="380549150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="388543800"/>
+    <pos x="7391400" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="388543800"/>
+    <pos x="9239250" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="388543800"/>
+    <pos x="11087100" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="388543800"/>
+    <pos x="12934950" y="388543800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5458,7 +5458,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/01_토너·미스트.xlsx
+++ b/카드_아키타입/01_토너·미스트.xlsx
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>장미 수증기 증류 / 장미의 수용성 성분함유</t>
+          <t>장미 수증기 증류 · 장미의 수용성 성분함유</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>라벤더, / 편백, 네롤리워터 등</t>
+          <t>라벤더 · 편백, 네롤리워터 등</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>유기농 아르간 오일에 천연레시틴을 / 이용한 리포좀 공법으로 제조하여 따로 계면활성제 없이 물 등의 수상에 쉽게 분산. / 단, 함량이 높으면 미스트가 물총처럼 분사됨.</t>
+          <t>유기농 아르간 오일에 천연레시틴을 · 이용한 리포좀 공법으로 제조하여 따로 계면활성제 없이 물 등의 수상에 쉽게 분산. · 단, 함량이 높으면 미스트가 물총처럼 분사됨.</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>아르간오일 2g, / 올리브리퀴드3g</t>
+          <t>아르간오일 2g · 올리브리퀴드3g</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>균번식 억제제, / 황금, 자몽씨추출물 등</t>
+          <t>균번식 억제제 · 황금, 자몽씨추출물 등</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>히아루론산, / 판테놀</t>
+          <t>히아루론산 · 판테놀</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>녹차, 어성초, / 오이추출물</t>
+          <t>녹차, 어성초 · 오이추출물</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>알로에베라워터,라벤더워터, / 카모마일워터 등.</t>
+          <t>알로에베라워터,라벤더워터 · 카모마일워터 등.</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>보습, 피부타입/계절에 따라 가감가능</t>
+          <t>보습, 피부타입 · 계절에 따라 가감가능</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (정제수의 양을 85g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (정제수의 양을 85g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>꽃중의 꽃이라는 말레이어. / 일랑일랑 꽃으로 에센셜오일을 (수증기)추출하는 과정에서 생기는 부산물, 일랑일랑의 수용성 성분이 다량 함유. 피부진정, / 피지 균형</t>
+          <t>꽃중의 꽃이라는 말레이어. · 일랑일랑 꽃으로 에센셜오일을 (수증기)추출하는 과정에서 생기는 부산물, 일랑일랑의 수용성 성분이 다량 함유. 피부진정 · 피지 균형</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>피부타입별로 / 원하는 워터 / 로즈워터, 네롤리워터, 편백워터, 로먼캐모마일, 티트리워터...</t>
+          <t>피부타입별로 · 원하는 워터 · 로즈워터, 네롤리워터, 편백워터, 로먼캐모마일, 티트리워터...</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>청국장의 끈~적 끈~적한 성분. / 자체보습, 천연보습인자생성촉진. 그로인해 피부보습을 한층강화 / 보습막을 입혀줌.</t>
+          <t>청국장의 끈~적 끈~적한 성분. · 자체보습, 천연보습인자생성촉진. 그로인해 피부보습을 한층강화 · 보습막을 입혀줌.</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>수용성 / 천연보존제</t>
+          <t>수용성 · 천연보존제</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>진한 로즈잎 증기추출,</t>
+          <t>진한 로즈잎 증기추출</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="F71" s="19" t="inlineStr">
         <is>
-          <t>헥산디올2g / (로즈마리워터를 62g으로 줄여주세요.)</t>
+          <t>헥산디올2g · (로즈마리워터를 62g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>페파민트 잎 증기추출,</t>
+          <t>페파민트 잎 증기추출</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 로즈마리워터</t>
+          <t>프리미엄 · 로즈마리워터</t>
         </is>
       </c>
     </row>
@@ -7294,12 +7294,12 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>프로판디올, Non GMO 옥수수 유래 보습 / 원하면 추가 가능. / 많은 양을 넣을 경우 스프레이 되지 않음.</t>
+          <t>프로판디올, Non GMO 옥수수 유래 보습 · 원하면 추가 가능. · 많은 양을 넣을 경우 스프레이 되지 않음.</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 리피듀어, / 식물성글리세린</t>
+          <t>히아루론산 · 리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>수용성 보존제는 1g / 나트로틱스일 경우 / 워터양을 1g / 줄이고 2g</t>
+          <t>수용성 보존제는 1g · 나트로틱스일 경우 · 워터양을 1g · 줄이고 2g</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="F95" s="19" t="inlineStr">
         <is>
-          <t>노화주름 관리를 원하면 EGF, FGF로 / 대체가능</t>
+          <t>노화주름 관리를 원하면 EGF, FGF로 · 대체가능</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 82g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 82g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
           <t>8가지 한약재를 호호바,해바라기오일, 비타민E에 우려낸 것.</t>
         </is>
       </c>
-      <c r="F99" s="19" t="n"/>
+      <c r="F99" s="19" t="inlineStr"/>
     </row>
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="14" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 78g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 78g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t>유비퀴논, 비타민 Q 라고 불림. / 심장, 피부 표피에 많은 양, / 20대를 기준으로 줄어듬.</t>
+          <t>유비퀴논, 비타민 Q 라고 불림. · 심장, 피부 표피에 많은 양 · 20대를 기준으로 줄어듬.</t>
         </is>
       </c>
       <c r="F123" s="19" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="F125" s="19" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="F126" s="19" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>(20방울) 에코인증, / 피부진정, 미백</t>
+          <t>(20방울) 에코인증 · 피부진정, 미백</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>(12방울) 감귤류, 피부진정. / 광독성 없음.</t>
+          <t>(12방울) 감귤류, 피부진정. · 광독성 없음.</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴 워터</t>
+          <t>원하는 · 플로럴 워터</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>인삼줄기세포, / 장미줄기세포 등</t>
+          <t>인삼줄기세포 · 장미줄기세포 등</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>낫또모이스트, / 판테놀, / 리피듀어, / 히아루론산 등</t>
+          <t>낫또모이스트 · 판테놀 · 리피듀어 · 히아루론산 등</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="E153" s="19" t="inlineStr">
         <is>
-          <t>탁월한 항산화, / 다마스크 장미 식물줄기세포</t>
+          <t>탁월한 항산화 · 다마스크 장미 식물줄기세포</t>
         </is>
       </c>
       <c r="F153" s="19" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F154" s="19" t="inlineStr">
         <is>
-          <t>낫또 모이스트, / 글리세린 등</t>
+          <t>낫또 모이스트 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>고보습,</t>
+          <t>고보습</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="F168" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 글리세린 등</t>
+          <t>히아루론산 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 31g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 31g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>레몬 , 레몬그라스, / 로즈우드에센셜 오일 블랜딩</t>
+          <t>레몬 , 레몬그라스 · 로즈우드에센셜 오일 블랜딩</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E179" s="19" t="inlineStr">
         <is>
-          <t>양조장 누룩의 본질이 사카로 미세스, 사카로마세스 안에는 수많은 발효 효모가 들어있고 그중에 하나가 갈락토미세스. / 풍부한 영양, 깊은보습</t>
+          <t>양조장 누룩의 본질이 사카로 미세스, 사카로마세스 안에는 수많은 발효 효모가 들어있고 그중에 하나가 갈락토미세스. · 풍부한 영양, 깊은보습</t>
         </is>
       </c>
       <c r="F179" s="19" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F182" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올5g / (로즈워터의 양을 167.5g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올5g · (로즈워터의 양을 167.5g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F192" s="10" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>병풀의 핵심 효능 성분, 진정. / 트러블 개선, / 피부 장벽 강화</t>
+          <t>병풀의 핵심 효능 성분, 진정. · 트러블 개선 · 피부 장벽 강화</t>
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F194" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="F195" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올 2g / (워터의 양을 93g으로 / 줄여주세요.)</t>
+          <t>1,2-헥산디올 2g · (워터의 양을 93g으로 · 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="E207" s="19" t="inlineStr">
         <is>
-          <t>테트라펩타이드-44, 쿠퍼펩타이드-1, / 헥사펩타이드-9, 화이트펩타이드-23로 / 구성된 4가지 복합 펩타이드,1000ppm / 트러블관리에 도움</t>
+          <t>테트라펩타이드-44, 쿠퍼펩타이드-1 · 헥사펩타이드-9, 화이트펩타이드-23로 · 구성된 4가지 복합 펩타이드,1000ppm · 트러블관리에 도움</t>
         </is>
       </c>
       <c r="F207" s="19" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="E208" s="19" t="inlineStr">
         <is>
-          <t>보습제, 분사력과 피부 타입에 맞게 / 조금씩 첨가하여 조절해주세요. / ※많은양 첨가할 경우 물총처럼 분사됨</t>
+          <t>보습제, 분사력과 피부 타입에 맞게 · 조금씩 첨가하여 조절해주세요. · ※많은양 첨가할 경우 물총처럼 분사됨</t>
         </is>
       </c>
       <c r="F208" s="19" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="F209" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈마리워터의 양을53g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈마리워터의 양을53g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="F218" s="10" t="inlineStr">
         <is>
-          <t>유기농 카밍 5솔루션, / 캐모마일, 카렌듈라 등.</t>
+          <t>유기농 카밍 5솔루션 · 캐모마일, 카렌듈라 등.</t>
         </is>
       </c>
     </row>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
-          <t>고중저분자, 트리플 히아루론산, / 용량 추가가능 점도가 있어 스프레이되지 않을 수도^^</t>
+          <t>고중저분자, 트리플 히아루론산 · 용량 추가가능 점도가 있어 스프레이되지 않을 수도^^</t>
         </is>
       </c>
       <c r="F221" s="10" t="inlineStr">
         <is>
-          <t>에코 / 보습제</t>
+          <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F222" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을83g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을83g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="F230" s="19" t="inlineStr">
         <is>
-          <t>편백워터, / 녹차워터</t>
+          <t>편백워터 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -10448,10 +10448,10 @@
       </c>
       <c r="E232" s="19" t="inlineStr">
         <is>
-          <t>민감성 피부를 위한 천연원료, / 로즈마리, 캐모마일, 녹차, 병풀, 감초, 호장근 복합 추출물</t>
-        </is>
-      </c>
-      <c r="F232" s="19" t="n"/>
+          <t>민감성 피부를 위한 천연원료 · 로즈마리, 캐모마일, 녹차, 병풀, 감초, 호장근 복합 추출물</t>
+        </is>
+      </c>
+      <c r="F232" s="19" t="inlineStr"/>
     </row>
     <row r="233" ht="64" customHeight="1">
       <c r="A233" s="19" t="inlineStr">
@@ -10656,10 +10656,10 @@
       </c>
       <c r="E243" s="10" t="inlineStr">
         <is>
-          <t>진정 수분공급. / 참마, 흰목이버섯, 미역, 알로에 / 복합추출성분</t>
-        </is>
-      </c>
-      <c r="F243" s="10" t="n"/>
+          <t>진정 수분공급. · 참마, 흰목이버섯, 미역, 알로에 · 복합추출성분</t>
+        </is>
+      </c>
+      <c r="F243" s="10" t="inlineStr"/>
     </row>
     <row r="244" ht="48" customHeight="1">
       <c r="A244" s="10" t="inlineStr">
@@ -10687,7 +10687,7 @@
           <t>소변, 땀 성분, 천연피부보습인자의 7% 성분, 보습, 각질연화 등</t>
         </is>
       </c>
-      <c r="F244" s="10" t="n"/>
+      <c r="F244" s="10" t="inlineStr"/>
     </row>
     <row r="245" ht="64" customHeight="1">
       <c r="A245" s="10" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="F245" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10859,12 +10859,12 @@
       </c>
       <c r="E254" s="19" t="inlineStr">
         <is>
-          <t>인체 흡수가 용이한 / 저분자화 순수 단백질 사용, / 18종의 아미노산으로 구성</t>
+          <t>인체 흡수가 용이한 · 저분자화 순수 단백질 사용 · 18종의 아미노산으로 구성</t>
         </is>
       </c>
       <c r="F254" s="19" t="inlineStr">
         <is>
-          <t>아카시아, / 마린콜라겐</t>
+          <t>아카시아 · 마린콜라겐</t>
         </is>
       </c>
     </row>
@@ -10891,10 +10891,10 @@
       </c>
       <c r="E255" s="19" t="inlineStr">
         <is>
-          <t>진정 수분공급. / 참마, 흰목이버섯, 미역, / 알로에 복합추출성분</t>
-        </is>
-      </c>
-      <c r="F255" s="19" t="n"/>
+          <t>진정 수분공급. · 참마, 흰목이버섯, 미역 · 알로에 복합추출성분</t>
+        </is>
+      </c>
+      <c r="F255" s="19" t="inlineStr"/>
     </row>
     <row r="256" ht="48" customHeight="1">
       <c r="A256" s="19" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="F256" s="19" t="inlineStr">
         <is>
-          <t>낫또모이스트, / 판테놀, / 리피듀어, / 히아루론산 등</t>
+          <t>낫또모이스트 · 판테놀 · 리피듀어 · 히아루론산 등</t>
         </is>
       </c>
     </row>
@@ -10951,12 +10951,12 @@
       </c>
       <c r="E257" s="19" t="inlineStr">
         <is>
-          <t>비타민B5, 보습 / ※많은양 첨가할 경우 / 물총처럼 분사됨</t>
+          <t>비타민B5, 보습 · ※많은양 첨가할 경우 · 물총처럼 분사됨</t>
         </is>
       </c>
       <c r="F257" s="19" t="inlineStr">
         <is>
-          <t>히아루론산, / 글리세린</t>
+          <t>히아루론산 · 글리세린</t>
         </is>
       </c>
     </row>
@@ -10983,12 +10983,12 @@
       </c>
       <c r="E258" s="19" t="inlineStr">
         <is>
-          <t>상큼한 레몬향, / 시트로네랄, 리나롤, 리모넨등 풍부</t>
+          <t>상큼한 레몬향 · 시트로네랄, 리나롤, 리모넨등 풍부</t>
         </is>
       </c>
       <c r="F258" s="19" t="inlineStr">
         <is>
-          <t>로즈워터, / 네롤리워터</t>
+          <t>로즈워터 · 네롤리워터</t>
         </is>
       </c>
     </row>
@@ -11047,12 +11047,12 @@
       </c>
       <c r="E260" s="19" t="inlineStr">
         <is>
-          <t>보습제, 자유수 억제, / 균번식억제</t>
+          <t>보습제, 자유수 억제 · 균번식억제</t>
         </is>
       </c>
       <c r="F260" s="19" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -11197,7 +11197,7 @@
       </c>
       <c r="E269" s="10" t="inlineStr">
         <is>
-          <t>호호바오일 리포좀화, / 수상에 쉽게 분산</t>
+          <t>호호바오일 리포좀화 · 수상에 쉽게 분산</t>
         </is>
       </c>
       <c r="F269" s="10" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="E271" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃수, 진정,</t>
+          <t>오렌지꽃수, 진정</t>
         </is>
       </c>
       <c r="F271" s="10" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -11293,12 +11293,12 @@
       </c>
       <c r="E272" s="10" t="inlineStr">
         <is>
-          <t>보습제, 자유수 억제, / 균번식억제</t>
+          <t>보습제, 자유수 억제 · 균번식억제</t>
         </is>
       </c>
       <c r="F272" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -11357,12 +11357,12 @@
       </c>
       <c r="E274" s="10" t="inlineStr">
         <is>
-          <t>로즈마리 잎,꽃 수, 수렴, / 피부장벽강화</t>
+          <t>로즈마리 잎,꽃 수, 수렴 · 피부장벽강화</t>
         </is>
       </c>
       <c r="F274" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="F284" s="19" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="E285" s="19" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F285" s="19" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="F296" s="10" t="inlineStr">
         <is>
-          <t>로먼 / 캐모마일워터</t>
+          <t>로먼 · 캐모마일워터</t>
         </is>
       </c>
     </row>
@@ -11841,10 +11841,10 @@
       </c>
       <c r="E298" s="10" t="inlineStr">
         <is>
-          <t>피부 생기를 위해 엄선한 / 11가지 비타민 컴플렉스</t>
-        </is>
-      </c>
-      <c r="F298" s="10" t="n"/>
+          <t>피부 생기를 위해 엄선한 · 11가지 비타민 컴플렉스</t>
+        </is>
+      </c>
+      <c r="F298" s="10" t="inlineStr"/>
     </row>
     <row r="299" ht="64" customHeight="1">
       <c r="A299" s="10" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="E299" s="10" t="inlineStr">
         <is>
-          <t>보습제, 자유수 억제, / 균번식억제</t>
+          <t>보습제, 자유수 억제 · 균번식억제</t>
         </is>
       </c>
       <c r="F299" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F308" s="19" t="inlineStr">
         <is>
-          <t>로먼 / 캐모마일워터</t>
+          <t>로먼 · 캐모마일워터</t>
         </is>
       </c>
     </row>
@@ -12030,10 +12030,10 @@
       </c>
       <c r="E309" s="19" t="inlineStr">
         <is>
-          <t>피부 생기, / 11가지 비타민 컴플렉스</t>
-        </is>
-      </c>
-      <c r="F309" s="19" t="n"/>
+          <t>피부 생기 · 11가지 비타민 컴플렉스</t>
+        </is>
+      </c>
+      <c r="F309" s="19" t="inlineStr"/>
     </row>
     <row r="310" ht="64" customHeight="1">
       <c r="A310" s="19" t="inlineStr">
@@ -12058,12 +12058,12 @@
       </c>
       <c r="E310" s="19" t="inlineStr">
         <is>
-          <t>보습제, 자유수 억제, / 균번식억제</t>
+          <t>보습제, 자유수 억제 · 균번식억제</t>
         </is>
       </c>
       <c r="F310" s="19" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 94g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 94g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="E319" s="10" t="inlineStr">
         <is>
-          <t>(유기농) 불가리아 장미 / 수증기 증류</t>
+          <t>(유기농) 불가리아 장미 · 수증기 증류</t>
         </is>
       </c>
       <c r="F319" s="10" t="inlineStr">
@@ -12229,12 +12229,12 @@
       </c>
       <c r="E320" s="10" t="inlineStr">
         <is>
-          <t>덱스판테놀 80% 함량, 비타민B5, 보습 재생, / 계절이나 피부타입에 따라 조절</t>
+          <t>덱스판테놀 80% 함량, 비타민B5, 보습 재생 · 계절이나 피부타입에 따라 조절</t>
         </is>
       </c>
       <c r="F320" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 글리세린 등</t>
+          <t>히아루론산 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="F332" s="19" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="E333" s="19" t="inlineStr">
         <is>
-          <t>감초의 수/지용성성분추출물.</t>
+          <t>감초의 수 · 지용성성분추출물.</t>
         </is>
       </c>
       <c r="F333" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F334" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (알로에워터를 87g으로 늘려주세요.)</t>
+          <t>1,2-헥산디올2g · (알로에워터를 87g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="F343" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="F344" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="F345" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="E355" s="19" t="inlineStr">
         <is>
-          <t>티트리 수증기 / 증류법으로 추출</t>
+          <t>티트리 수증기 · 증류법으로 추출</t>
         </is>
       </c>
       <c r="F355" s="19" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="E367" s="10" t="inlineStr">
         <is>
-          <t>보성 무농약 녹차, / 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
+          <t>보성 무농약 녹차 · 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
         </is>
       </c>
       <c r="F367" s="10" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="F368" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -13207,7 +13207,7 @@
       </c>
       <c r="F369" s="10" t="inlineStr">
         <is>
-          <t>수용성보존제, / 나트로틱스2g / (워터 1g 줄이기</t>
+          <t>수용성보존제 · 나트로틱스2g · (워터 1g 줄이기</t>
         </is>
       </c>
     </row>
@@ -13237,7 +13237,7 @@
           <t>자외선UV-B를 주로 난반사</t>
         </is>
       </c>
-      <c r="F370" s="10" t="n"/>
+      <c r="F370" s="10" t="inlineStr"/>
     </row>
     <row r="371" ht="32" customHeight="1">
       <c r="A371" s="10" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="E381" s="19" t="inlineStr">
         <is>
-          <t>오렌지꽃을 수증기증류하여 에센셜오일을 추출하는 과정에서 생기는 부산물, 베이비, 노화피부에 사용,</t>
+          <t>오렌지꽃을 수증기증류하여 에센셜오일을 추출하는 과정에서 생기는 부산물, 베이비, 노화피부에 사용</t>
         </is>
       </c>
       <c r="F381" s="19" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="F383" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 29g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 29g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="F396" s="10" t="inlineStr">
         <is>
-          <t>EGF,아데노신, / 달팽이추출물 등</t>
+          <t>EGF,아데노신 · 달팽이추출물 등</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="F397" s="10" t="inlineStr">
         <is>
-          <t>아카시아콜라겐, / 플라센타 등</t>
+          <t>아카시아콜라겐 · 플라센타 등</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="F399" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 79g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 79g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="F410" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 77g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 77g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="E423" s="10" t="inlineStr">
         <is>
-          <t>장미꽃잎을 수증기증류함. / 장미의 수용성 성분 다량함유 수분공급, 진정</t>
+          <t>장미꽃잎을 수증기증류함. · 장미의 수용성 성분 다량함유 수분공급, 진정</t>
         </is>
       </c>
       <c r="F423" s="10" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="E424" s="10" t="inlineStr">
         <is>
-          <t>로먼캐모마일꽃을 수증기 증류함. / 수용성 성분다량함유,수분공급 진정</t>
+          <t>로먼캐모마일꽃을 수증기 증류함. · 수용성 성분다량함유,수분공급 진정</t>
         </is>
       </c>
       <c r="F424" s="10" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="E425" s="10" t="inlineStr">
         <is>
-          <t>보톡스펩타이드이라고 불림. / 전체양의 3~10%사용. / 아래 설명참고</t>
+          <t>보톡스펩타이드이라고 불림. · 전체양의 3~10%사용. · 아래 설명참고</t>
         </is>
       </c>
       <c r="F425" s="10" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="F426" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로먼캐모마일워터의 양을 24g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로먼캐모마일워터의 양을 24g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14641,7 @@
       </c>
       <c r="E436" s="19" t="inlineStr">
         <is>
-          <t>장미꽃잎을 수증기증류함. / 장미의 수용성 성분 다량함유 수분공급, 진정</t>
+          <t>장미꽃잎을 수증기증류함. · 장미의 수용성 성분 다량함유 수분공급, 진정</t>
         </is>
       </c>
       <c r="F436" s="19" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="F439" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 30g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 30g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="F452" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (편백워터의 양을 30g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (편백워터의 양을 30g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="F462" s="19" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="F464" s="19" t="inlineStr">
         <is>
-          <t>아르간 등 / 베이스오일</t>
+          <t>아르간 등 · 베이스오일</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="F465" s="19" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="F466" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (정제수의 양을 85g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (정제수의 양을 85g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15396,7 @@
           <t>피부타입별 추출물 참고</t>
         </is>
       </c>
-      <c r="F468" s="19" t="n"/>
+      <c r="F468" s="19" t="inlineStr"/>
     </row>
     <row r="469" ht="14" customHeight="1">
       <c r="A469" s="14" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 44g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 44g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="F480" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="F490" s="19" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="F493" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (라벤더워터의 양을 25g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (라벤더워터의 양을 25g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="E503" s="10" t="inlineStr">
         <is>
-          <t>장미 수증기추출법으로 추출, / 장미의 수용성 성분 다량 함유</t>
+          <t>장미 수증기추출법으로 추출 · 장미의 수용성 성분 다량 함유</t>
         </is>
       </c>
       <c r="F503" s="10" t="inlineStr">
@@ -16185,7 +16185,7 @@
       </c>
       <c r="F506" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 69g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 69g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="E516" s="19" t="inlineStr">
         <is>
-          <t>편백 잎을 수증기추출, 피톤치드 함유, 수분공급,</t>
+          <t>편백 잎을 수증기추출, 피톤치드 함유, 수분공급</t>
         </is>
       </c>
       <c r="F516" s="19" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="E518" s="19" t="inlineStr">
         <is>
-          <t>USDA Organic 유기농 인증. / 유기농 청호추출물, 카렌듈라꽃추출물, 컴프리잎추출물, 에버라스팅추출물, / 님잎추출물. 허브 5 가지 추출물 / 각종 트러블 증상에 효과적이고 독성이나 자극이 없음. 피부면역력 강화와 피부개선</t>
+          <t>USDA Organic 유기농 인증. · 유기농 청호추출물, 카렌듈라꽃추출물, 컴프리잎추출물, 에버라스팅추출물 · 님잎추출물. 허브 5 가지 추출물 · 각종 트러블 증상에 효과적이고 독성이나 자극이 없음. 피부면역력 강화와 피부개선</t>
         </is>
       </c>
       <c r="F518" s="19" t="inlineStr">
         <is>
-          <t>피부타입에 맞는 / 추출물 대체가능</t>
+          <t>피부타입에 맞는 · 추출물 대체가능</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="F520" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (편백워터의 양을 64g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (편백워터의 양을 64g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="E530" s="10" t="inlineStr">
         <is>
-          <t>허브의 여왕, 수증기증류추출 / 진정, 트러블완화</t>
+          <t>허브의 여왕, 수증기증류추출 · 진정, 트러블완화</t>
         </is>
       </c>
       <c r="F530" s="10" t="inlineStr">
@@ -16736,12 +16736,12 @@
       </c>
       <c r="E532" s="10" t="inlineStr">
         <is>
-          <t>알란토인 100% / 컴프리뿌리추출, 진정, 염증관리. / 0.3 %이상 사용시 침전생김</t>
+          <t>알란토인 100% · 컴프리뿌리추출, 진정, 염증관리. · 0.3 %이상 사용시 침전생김</t>
         </is>
       </c>
       <c r="F532" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16837,7 @@
       </c>
       <c r="F535" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (편백워터의 양을 34g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (편백워터의 양을 34g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16990,12 +16990,12 @@
       </c>
       <c r="E545" s="19" t="inlineStr">
         <is>
-          <t>보성 무농약 녹차, / 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
+          <t>보성 무농약 녹차 · 식물성 에탄올에 저온추출, 감압농축, 동결건조하여 유효성분을 많이 포함하고 있습니다. 폴리페놀 함량이 3배높고 항산화 작용</t>
         </is>
       </c>
       <c r="F545" s="19" t="inlineStr">
         <is>
-          <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
+          <t>녹소초 추출물 · 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17049,7 @@
           <t>항산화 폴리페놀 성분</t>
         </is>
       </c>
-      <c r="F547" s="19" t="n"/>
+      <c r="F547" s="19" t="inlineStr"/>
     </row>
     <row r="548" ht="80" customHeight="1">
       <c r="A548" s="19" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="E548" s="19" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F548" s="19" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
           <t>인삼 추출물</t>
         </is>
       </c>
-      <c r="F554" s="10" t="n"/>
+      <c r="F554" s="10" t="inlineStr"/>
     </row>
     <row r="555" ht="48" customHeight="1">
       <c r="A555" s="10" t="inlineStr">
@@ -17250,12 +17250,12 @@
       </c>
       <c r="E557" s="10" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F557" s="10" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
           <t>레드와인(폴리페놀·레스베라트롤), 항산화</t>
         </is>
       </c>
-      <c r="F565" s="19" t="n"/>
+      <c r="F565" s="19" t="inlineStr"/>
     </row>
     <row r="566" ht="48" customHeight="1">
       <c r="A566" s="19" t="inlineStr">
@@ -17418,12 +17418,12 @@
       </c>
       <c r="E567" s="19" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F567" s="19" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E575" s="10" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F575" s="10" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -17600,7 +17600,7 @@
       </c>
       <c r="E576" s="10" t="inlineStr">
         <is>
-          <t>티로시나아제 억제를 통한 / 기미, 잡티, 색소침착 개선</t>
+          <t>티로시나아제 억제를 통한 · 기미, 잡티, 색소침착 개선</t>
         </is>
       </c>
       <c r="F576" s="10" t="inlineStr">
@@ -17731,7 +17731,7 @@
           <t>인삼 추출물</t>
         </is>
       </c>
-      <c r="F583" s="19" t="n"/>
+      <c r="F583" s="19" t="inlineStr"/>
     </row>
     <row r="584" ht="64" customHeight="1">
       <c r="A584" s="19" t="inlineStr">
@@ -17780,12 +17780,12 @@
       </c>
       <c r="E585" s="19" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F585" s="19" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
           <t>피부톤을 밝고 매끄럽게 하는데 도움</t>
         </is>
       </c>
-      <c r="F586" s="19" t="n"/>
+      <c r="F586" s="19" t="inlineStr"/>
     </row>
     <row r="587" ht="32" customHeight="1">
       <c r="A587" s="19" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="E587" s="19" t="inlineStr">
         <is>
-          <t>티로시나아제 억제를 통한 / 기미, 잡티, 색소침착 개선</t>
+          <t>티로시나아제 억제를 통한 · 기미, 잡티, 색소침착 개선</t>
         </is>
       </c>
       <c r="F587" s="19" t="inlineStr">
@@ -17973,12 +17973,12 @@
       </c>
       <c r="E595" s="10" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F595" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="E597" s="10" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
+          <t>귤껍질오일 · 임신기간 영아에게 안전하게 사용 · 모든 피부사용</t>
         </is>
       </c>
       <c r="F597" s="10" t="inlineStr">
@@ -18090,7 +18090,7 @@
       </c>
       <c r="F599" s="10" t="inlineStr">
         <is>
-          <t>로즈3% in 호호바오일 / 10방울 또는 / 로즈우드, 로즈제라늄 등 / 원하는 에센셜오일</t>
+          <t>로즈3% in 호호바오일 · 10방울 또는 · 로즈우드, 로즈제라늄 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -18113,12 +18113,12 @@
       </c>
       <c r="E600" s="10" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F600" s="10" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
           <t>히비스커스 추출, 항산화·천연 AHA 유사</t>
         </is>
       </c>
-      <c r="F609" s="19" t="n"/>
+      <c r="F609" s="19" t="inlineStr"/>
     </row>
     <row r="610" ht="48" customHeight="1">
       <c r="A610" s="19" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="E611" s="19" t="inlineStr">
         <is>
-          <t>보습제, 겨울철, / 아주 건성의 경우 첨가</t>
+          <t>보습제, 겨울철 · 아주 건성의 경우 첨가</t>
         </is>
       </c>
       <c r="F611" s="19" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="E619" s="10" t="inlineStr">
         <is>
-          <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. 임상시 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. / '바르는 보톡스' 등으로 인기</t>
+          <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. 임상시 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. · '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
       <c r="F619" s="10" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="E620" s="10" t="inlineStr">
         <is>
-          <t>녹황색채소에 존재, 비타민B3, 피부장벽강화, / 식약청인증 미백원료.피부트러블관리효과</t>
+          <t>녹황색채소에 존재, 비타민B3, 피부장벽강화 · 식약청인증 미백원료.피부트러블관리효과</t>
         </is>
       </c>
       <c r="F620" s="10" t="inlineStr">
@@ -18520,12 +18520,12 @@
       </c>
       <c r="E621" s="10" t="inlineStr">
         <is>
-          <t>7가지 유기농 현미와 야채 추출물,</t>
+          <t>7가지 유기농 현미와 야채 추출물</t>
         </is>
       </c>
       <c r="F621" s="10" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="F623" s="10" t="inlineStr">
         <is>
-          <t>리피듀어, 판테놀, / 히아루론산</t>
+          <t>리피듀어, 판테놀 · 히아루론산</t>
         </is>
       </c>
     </row>
@@ -18616,12 +18616,12 @@
       </c>
       <c r="E624" s="10" t="inlineStr">
         <is>
-          <t>장미잎을 수증기증류, / 장미꽃잎의 수용성 성분 다량함유.</t>
+          <t>장미잎을 수증기증류 · 장미꽃잎의 수용성 성분 다량함유.</t>
         </is>
       </c>
       <c r="F624" s="10" t="inlineStr">
         <is>
-          <t>네롤리워터 등 / 플로랄워터</t>
+          <t>네롤리워터 등 · 플로랄워터</t>
         </is>
       </c>
     </row>
@@ -18814,7 +18814,7 @@
           <t>천연항균물질인 멜리틴함유. 벌을 죽이지 않고 벌독 채취, 약간의 전기자극을 주고 유리판에 벌독을 쏘게해 채취.벌침은 류마티즘 등에 많이 사용. 피부적용시 여드름균, 무좀 등을 관리.</t>
         </is>
       </c>
-      <c r="F635" s="19" t="n"/>
+      <c r="F635" s="19" t="inlineStr"/>
     </row>
     <row r="636" ht="64" customHeight="1">
       <c r="A636" s="19" t="inlineStr">
@@ -18908,7 +18908,7 @@
       </c>
       <c r="F638" s="19" t="inlineStr">
         <is>
-          <t>히아루론산, / 낫또모이스트, / 에코보습제 등</t>
+          <t>히아루론산 · 낫또모이스트 · 에코보습제 등</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="E663" s="19" t="inlineStr">
         <is>
-          <t>식물성 보습제, / 피부진정, 재생</t>
+          <t>식물성 보습제 · 피부진정, 재생</t>
         </is>
       </c>
       <c r="F663" s="19" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="F664" s="19" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -19604,12 +19604,12 @@
       </c>
       <c r="E673" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃 증류수 / 매끈한 피부결 도움</t>
+          <t>오렌지꽃 증류수 · 매끈한 피부결 도움</t>
         </is>
       </c>
       <c r="F673" s="10" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
           <t>연어DNA, 항염, 재생</t>
         </is>
       </c>
-      <c r="F674" s="10" t="n"/>
+      <c r="F674" s="10" t="inlineStr"/>
     </row>
     <row r="675" ht="16" customHeight="1">
       <c r="A675" s="10" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="F675" s="10" t="inlineStr">
         <is>
-          <t>에코 / 보습제</t>
+          <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="F676" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -19857,10 +19857,10 @@
       </c>
       <c r="E686" s="19" t="inlineStr">
         <is>
-          <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
-        </is>
-      </c>
-      <c r="F686" s="19" t="n"/>
+          <t>비타민C의 장점은 살리고 단점은 보완 · 식약처 미백 고시 원료, 미백, 탄력</t>
+        </is>
+      </c>
+      <c r="F686" s="19" t="inlineStr"/>
     </row>
     <row r="687" ht="48" customHeight="1">
       <c r="A687" s="19" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="F688" s="19" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="F689" s="19" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -20050,7 +20050,7 @@
       </c>
       <c r="F692" s="19" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
